--- a/data/trans_dic/P16A12-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A12-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,26</t>
+          <t>4,71; 8,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,14</t>
+          <t>4,98; 9,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,72; 12,45</t>
+          <t>7,66; 12,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 11,59</t>
+          <t>7,8; 11,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,71</t>
+          <t>3,43; 6,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,24</t>
+          <t>5,32; 9,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,52; 11,06</t>
+          <t>6,67; 11,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,74; 10,88</t>
+          <t>7,76; 10,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,88</t>
+          <t>4,5; 6,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 8,61</t>
+          <t>5,76; 8,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,69; 10,85</t>
+          <t>7,8; 11,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,26; 10,73</t>
+          <t>8,28; 10,69</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,04</t>
+          <t>4,83; 7,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 8,28</t>
+          <t>5,07; 8,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 9,54</t>
+          <t>6,39; 9,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,81</t>
+          <t>3,23; 8,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 9,4</t>
+          <t>5,98; 9,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,44; 9,77</t>
+          <t>6,41; 9,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,93; 9,48</t>
+          <t>5,99; 9,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 8,89</t>
+          <t>6,46; 8,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 8,04</t>
+          <t>5,72; 8,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,5</t>
+          <t>6,1; 8,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 9,21</t>
+          <t>6,6; 8,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,27</t>
+          <t>4,63; 8,28</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,43</t>
+          <t>3,24; 6,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,44</t>
+          <t>4,71; 8,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 11,57</t>
+          <t>7,09; 11,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,1; 9,97</t>
+          <t>6,08; 9,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,05</t>
+          <t>4,29; 7,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 10,68</t>
+          <t>6,55; 10,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,85</t>
+          <t>5,72; 9,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,41</t>
+          <t>2,12; 6,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,63</t>
+          <t>4,22; 6,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,99</t>
+          <t>6,24; 9,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 10,12</t>
+          <t>7,02; 10,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,44</t>
+          <t>3,95; 7,46</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 6,62</t>
+          <t>4,17; 6,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,44; 11,53</t>
+          <t>7,13; 11,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 8,88</t>
+          <t>5,75; 8,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,81; 11,19</t>
+          <t>7,82; 11,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,1</t>
+          <t>4,27; 7,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,87</t>
+          <t>8,18; 11,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,42</t>
+          <t>6,08; 9,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,26</t>
+          <t>5,42; 8,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 6,44</t>
+          <t>4,54; 6,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,28; 10,82</t>
+          <t>8,3; 11,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 8,85</t>
+          <t>6,35; 8,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,97; 9,13</t>
+          <t>6,83; 9,08</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 6,39</t>
+          <t>4,86; 6,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,41; 8,27</t>
+          <t>6,46; 8,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,46; 9,33</t>
+          <t>7,45; 9,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,44; 9,24</t>
+          <t>6,12; 9,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,02</t>
+          <t>5,29; 6,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,59; 9,45</t>
+          <t>7,52; 9,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,84</t>
+          <t>6,98; 8,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,66</t>
+          <t>5,68; 7,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,38</t>
+          <t>5,3; 6,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,21; 8,6</t>
+          <t>7,22; 8,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,77</t>
+          <t>7,46; 8,79</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,61; 8,28</t>
+          <t>6,48; 8,24</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31594; 57264</t>
+          <t>32641; 56684</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36748; 64033</t>
+          <t>34894; 63516</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52125; 84010</t>
+          <t>51692; 81115</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49114; 73634</t>
+          <t>49557; 73760</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23419; 46216</t>
+          <t>23602; 45296</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37154; 64161</t>
+          <t>36956; 64543</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43896; 74429</t>
+          <t>44871; 77300</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52288; 73517</t>
+          <t>52426; 73950</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61915; 95009</t>
+          <t>62189; 94306</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>80542; 120082</t>
+          <t>80294; 119632</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103688; 146201</t>
+          <t>105076; 148200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>108360; 140672</t>
+          <t>108521; 140186</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46223; 77316</t>
+          <t>46418; 75511</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52005; 84327</t>
+          <t>51629; 83407</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64812; 97524</t>
+          <t>65342; 98527</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41196; 105094</t>
+          <t>38550; 103309</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57925; 91004</t>
+          <t>57868; 93203</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66173; 100453</t>
+          <t>65839; 101744</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61825; 98899</t>
+          <t>62512; 98597</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>61250; 85157</t>
+          <t>61893; 85825</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>111808; 155250</t>
+          <t>110431; 155463</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>122609; 173808</t>
+          <t>124729; 172176</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136860; 190196</t>
+          <t>136279; 183782</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>98260; 177888</t>
+          <t>99687; 178031</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21787; 43634</t>
+          <t>22016; 43909</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35996; 63853</t>
+          <t>35660; 64624</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54621; 87874</t>
+          <t>53876; 86950</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42929; 70129</t>
+          <t>42749; 68965</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30383; 55072</t>
+          <t>29357; 54380</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51895; 82923</t>
+          <t>50848; 83088</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46057; 77329</t>
+          <t>44877; 77743</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21854; 59748</t>
+          <t>19799; 60088</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57713; 90328</t>
+          <t>57545; 91371</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>93564; 137818</t>
+          <t>95709; 140461</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110416; 156365</t>
+          <t>108476; 156027</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66376; 121829</t>
+          <t>64569; 122063</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37835; 62388</t>
+          <t>39284; 63680</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70411; 109036</t>
+          <t>67428; 107208</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53742; 83274</t>
+          <t>53902; 83852</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72376; 103673</t>
+          <t>72444; 105480</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42998; 73791</t>
+          <t>44329; 74043</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>83770; 124481</t>
+          <t>85774; 123936</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61478; 98318</t>
+          <t>63479; 98992</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58935; 90148</t>
+          <t>59165; 88478</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>88150; 127583</t>
+          <t>89909; 127947</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>165170; 215884</t>
+          <t>165558; 221671</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>126818; 175308</t>
+          <t>125912; 172943</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>140616; 184215</t>
+          <t>137925; 183167</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>158970; 209442</t>
+          <t>159289; 209717</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>219446; 282832</t>
+          <t>221138; 284347</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>253157; 316850</t>
+          <t>252972; 316276</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>222751; 319679</t>
+          <t>211549; 319523</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>177613; 237097</t>
+          <t>178922; 234057</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>269319; 335355</t>
+          <t>266721; 333511</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>246106; 313433</t>
+          <t>247421; 316075</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>203062; 280081</t>
+          <t>207611; 281874</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>349023; 424353</t>
+          <t>352733; 426803</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>502682; 599412</t>
+          <t>502880; 592595</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>517317; 608821</t>
+          <t>517427; 610129</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>470477; 588927</t>
+          <t>461231; 586496</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A12-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A12-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,18</t>
+          <t>4,63; 8,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,06</t>
+          <t>5,17; 9,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,02</t>
+          <t>7,43; 12,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,8; 11,61</t>
+          <t>7,49; 11,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,58</t>
+          <t>3,36; 6,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,3</t>
+          <t>5,28; 9,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 11,49</t>
+          <t>6,6; 11,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,76; 10,94</t>
+          <t>7,7; 10,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,83</t>
+          <t>4,45; 6,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,58</t>
+          <t>5,65; 8,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,8; 11,0</t>
+          <t>7,65; 10,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 10,69</t>
+          <t>8,25; 10,71</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 7,85</t>
+          <t>4,87; 8,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,19</t>
+          <t>5,19; 8,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 9,64</t>
+          <t>6,36; 9,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,66</t>
+          <t>6,78; 9,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 9,62</t>
+          <t>5,93; 9,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 9,9</t>
+          <t>6,56; 9,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 9,45</t>
+          <t>5,92; 9,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,46; 8,96</t>
+          <t>6,47; 8,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 8,05</t>
+          <t>5,78; 8,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,42</t>
+          <t>6,06; 8,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 8,9</t>
+          <t>6,55; 8,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,28</t>
+          <t>7,0; 8,97</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,47</t>
+          <t>3,21; 6,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,54</t>
+          <t>4,8; 8,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 11,45</t>
+          <t>7,29; 11,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,8</t>
+          <t>6,24; 9,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,95</t>
+          <t>4,42; 7,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,7</t>
+          <t>6,49; 10,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,9</t>
+          <t>5,85; 9,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,44</t>
+          <t>4,62; 7,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,71</t>
+          <t>4,22; 6,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 9,16</t>
+          <t>6,28; 9,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 10,1</t>
+          <t>7,28; 10,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,46</t>
+          <t>5,88; 8,05</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,76</t>
+          <t>3,91; 6,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,33</t>
+          <t>7,49; 11,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,75; 8,94</t>
+          <t>5,79; 8,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 11,38</t>
+          <t>7,68; 10,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,13</t>
+          <t>4,19; 6,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,18; 11,82</t>
+          <t>8,13; 11,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,48</t>
+          <t>6,07; 9,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,11</t>
+          <t>6,11; 8,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,46</t>
+          <t>4,52; 6,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 11,11</t>
+          <t>8,34; 10,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 8,73</t>
+          <t>6,25; 8,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,83; 9,08</t>
+          <t>7,22; 9,3</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,4</t>
+          <t>4,83; 6,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 8,31</t>
+          <t>6,37; 8,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,32</t>
+          <t>7,44; 9,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 9,24</t>
+          <t>7,86; 9,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 6,93</t>
+          <t>5,24; 6,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 9,4</t>
+          <t>7,53; 9,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 8,92</t>
+          <t>6,92; 8,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 7,71</t>
+          <t>6,83; 8,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,41</t>
+          <t>5,3; 6,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 8,5</t>
+          <t>7,27; 8,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,79</t>
+          <t>7,46; 8,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,24</t>
+          <t>7,51; 8,6</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61105</t>
+          <t>65891</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>62733</t>
+          <t>66671</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>123839</t>
+          <t>132562</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32641; 56684</t>
+          <t>32067; 57546</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34894; 63516</t>
+          <t>36262; 64207</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51692; 81115</t>
+          <t>50152; 81335</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49557; 73760</t>
+          <t>51702; 80773</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23602; 45296</t>
+          <t>23104; 46276</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36956; 64543</t>
+          <t>36674; 64449</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44871; 77300</t>
+          <t>44387; 74974</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52426; 73950</t>
+          <t>56477; 77491</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62189; 94306</t>
+          <t>61522; 96185</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>80294; 119632</t>
+          <t>78873; 117654</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>105076; 148200</t>
+          <t>103143; 145407</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>108521; 140186</t>
+          <t>117463; 152494</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77779</t>
+          <t>86499</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>73395</t>
+          <t>80802</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>151174</t>
+          <t>167301</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46418; 75511</t>
+          <t>46815; 78563</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51629; 83407</t>
+          <t>52806; 83796</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65342; 98527</t>
+          <t>64991; 99768</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38550; 103309</t>
+          <t>71114; 104029</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57868; 93203</t>
+          <t>57429; 90670</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65839; 101744</t>
+          <t>67385; 102283</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62512; 98597</t>
+          <t>61701; 98342</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>61893; 85825</t>
+          <t>69264; 94669</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>110431; 155463</t>
+          <t>111480; 156425</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>124729; 172176</t>
+          <t>123954; 172188</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136279; 183782</t>
+          <t>135316; 185558</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>99687; 178031</t>
+          <t>148482; 190059</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55605</t>
+          <t>62678</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42932</t>
+          <t>47588</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98536</t>
+          <t>110266</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22016; 43909</t>
+          <t>21752; 43630</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35660; 64624</t>
+          <t>36327; 64725</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53876; 86950</t>
+          <t>55347; 89431</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42749; 68965</t>
+          <t>50024; 79666</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29357; 54380</t>
+          <t>30240; 54185</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50848; 83088</t>
+          <t>50415; 82420</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44877; 77743</t>
+          <t>45921; 76611</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19799; 60088</t>
+          <t>37526; 58408</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57545; 91371</t>
+          <t>57426; 90416</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95709; 140461</t>
+          <t>96223; 138401</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>108476; 156027</t>
+          <t>112498; 159799</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64569; 122063</t>
+          <t>94916; 129901</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87620</t>
+          <t>91089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>74657</t>
+          <t>82185</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>162277</t>
+          <t>173274</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39284; 63680</t>
+          <t>36878; 62920</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67428; 107208</t>
+          <t>70874; 108311</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53902; 83852</t>
+          <t>54321; 84054</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72444; 105480</t>
+          <t>76079; 107828</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44329; 74043</t>
+          <t>43534; 72097</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>85774; 123936</t>
+          <t>85250; 122817</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>63479; 98992</t>
+          <t>63398; 97690</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59165; 88478</t>
+          <t>68289; 96203</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89909; 127947</t>
+          <t>89587; 128139</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>165558; 221671</t>
+          <t>166344; 219231</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125912; 172943</t>
+          <t>123844; 171510</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>137925; 183167</t>
+          <t>152230; 195991</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>282108</t>
+          <t>306157</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>253717</t>
+          <t>277246</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>535825</t>
+          <t>583403</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>159289; 209717</t>
+          <t>158228; 209691</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>221138; 284347</t>
+          <t>218039; 282352</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>252972; 316276</t>
+          <t>252521; 313703</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>211549; 319523</t>
+          <t>277521; 339357</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>178922; 234057</t>
+          <t>177006; 231537</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>266721; 333511</t>
+          <t>267237; 332385</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>247421; 316075</t>
+          <t>245451; 315598</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>207611; 281874</t>
+          <t>254897; 304505</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>352733; 426803</t>
+          <t>352579; 428694</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>502880; 592595</t>
+          <t>506456; 597037</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>517427; 610129</t>
+          <t>517451; 605904</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>461231; 586496</t>
+          <t>545388; 624473</t>
         </is>
       </c>
     </row>
